--- a/testing_reports/appium_app/reports/Mobile_Test_Execution_Report.xlsx
+++ b/testing_reports/appium_app/reports/Mobile_Test_Execution_Report.xlsx
@@ -640,7 +640,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Saveetha Dental College &amp; Hospital  •  Generated: 14 July 2026  |  14:35:05 (100% Pass)</t>
+          <t>Saveetha Dental College &amp; Hospital  •  Generated: 14 July 2026  |  17:16:17 (100% Pass)</t>
         </is>
       </c>
     </row>
